--- a/public/tridy.xlsx
+++ b/public/tridy.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\instaluju\Documents\Motol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D6E9B5-F8C9-4BAA-B4DC-EE8D1BD0212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343CE413-61E3-4ACA-A3CA-A780039FA0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1730" yWindow="590" windowWidth="12050" windowHeight="10410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6810" yWindow="1020" windowWidth="12050" windowHeight="10410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3A" sheetId="2" r:id="rId1"/>
-    <sheet name="3A_a" sheetId="4" r:id="rId2"/>
-    <sheet name="3A_b" sheetId="5" r:id="rId3"/>
-    <sheet name="1E" sheetId="3" r:id="rId4"/>
+    <sheet name="1E" sheetId="3" r:id="rId2"/>
+    <sheet name="3A_a" sheetId="4" r:id="rId3"/>
+    <sheet name="3A_b" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -748,7 +748,7 @@
   <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.5">
@@ -915,6 +915,137 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.5">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.5">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.5">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.5">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.5">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.5">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.5">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.5">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.5">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.5">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.5">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.5">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.5">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.5">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.5">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.5">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.5">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.5">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.5">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.5">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.5">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.5">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:A23" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE469823-409F-4510-9D6D-062E831698A5}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.5"/>
@@ -1060,10 +1191,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4113AD-B323-4242-B71C-08EA5415FB9F}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.5"/>
+  <cols>
+    <col min="1" max="1" width="9.58203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1185,135 +1320,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.5">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.5">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.5">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.5">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.5">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="15.5">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.5">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.5">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.5">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.5">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="15.5">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="15.5">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="15.5">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="15.5">
-      <c r="A15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="15.5">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.5">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="15.5">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.5">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="15.5">
-      <c r="A20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="15.5">
-      <c r="A21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="15.5">
-      <c r="A22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="15.5">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:A23" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
 </file>